--- a/notebooks_senales/tablas_prism_mixto.xlsx
+++ b/notebooks_senales/tablas_prism_mixto.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W6"/>
+  <dimension ref="A1:V6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,7 +472,7 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>CTR</t>
+          <t>EXP</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
@@ -521,11 +521,6 @@
         </is>
       </c>
       <c r="V1" t="inlineStr">
-        <is>
-          <t>EXP</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
         <is>
           <t>EXP</t>
         </is>
@@ -589,60 +584,55 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CTR_54</t>
+          <t>EXP_60</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>EXP_60</t>
+          <t>EXP_61</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>EXP_61</t>
+          <t>EXP_65</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>EXP_65</t>
+          <t>EXP_66</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>EXP_66</t>
+          <t>EXP_70</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>EXP_70</t>
+          <t>EXP_71</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>EXP_71</t>
+          <t>EXP_73</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>EXP_73</t>
+          <t>EXP_74</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>EXP_74</t>
+          <t>EXP_75</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>EXP_75</t>
+          <t>EXP_78</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
-        <is>
-          <t>EXP_78</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
         <is>
           <t>EXP_80</t>
         </is>
@@ -655,70 +645,67 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-10.3303</v>
+        <v>-10.2849</v>
       </c>
       <c r="C3" t="n">
-        <v>-10.6501</v>
+        <v>-10.5173</v>
       </c>
       <c r="D3" t="n">
-        <v>-8.942500000000001</v>
+        <v>-9.1554</v>
       </c>
       <c r="E3" t="n">
-        <v>-10.3656</v>
+        <v>-10.2096</v>
       </c>
       <c r="F3" t="n">
-        <v>-10.5361</v>
+        <v>-10.5576</v>
       </c>
       <c r="G3" t="n">
-        <v>-10.923</v>
+        <v>-10.8826</v>
       </c>
       <c r="H3" t="n">
-        <v>-10.2795</v>
+        <v>-10.156</v>
       </c>
       <c r="I3" t="n">
-        <v>-10.12</v>
+        <v>-10.1195</v>
       </c>
       <c r="J3" t="n">
-        <v>-10.3319</v>
+        <v>-10.3811</v>
       </c>
       <c r="K3" t="n">
-        <v>-10.6569</v>
+        <v>-10.5467</v>
       </c>
       <c r="L3" t="n">
-        <v>-4.2841</v>
+        <v>-10.6995</v>
       </c>
       <c r="M3" t="n">
-        <v>-10.8007</v>
+        <v>-10.2588</v>
       </c>
       <c r="N3" t="n">
-        <v>-10.3442</v>
+        <v>-10.7926</v>
       </c>
       <c r="O3" t="n">
-        <v>-10.8633</v>
+        <v>-10.5809</v>
       </c>
       <c r="P3" t="n">
-        <v>-10.6539</v>
+        <v>-10.3374</v>
       </c>
       <c r="Q3" t="n">
-        <v>-10.4452</v>
+        <v>-10.4672</v>
       </c>
       <c r="R3" t="n">
-        <v>-10.517</v>
+        <v>-10.3495</v>
       </c>
       <c r="S3" t="n">
-        <v>-10.4311</v>
+        <v>-10.2244</v>
       </c>
       <c r="T3" t="n">
-        <v>-10.4092</v>
+        <v>-10.3907</v>
       </c>
       <c r="U3" t="n">
-        <v>-10.4402</v>
+        <v>-11.1078</v>
       </c>
       <c r="V3" t="n">
-        <v>-11.1386</v>
-      </c>
-      <c r="W3" t="n">
-        <v>-10.8172</v>
+        <v>-10.8117</v>
       </c>
     </row>
     <row r="4">
@@ -728,70 +715,67 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-10.6652</v>
+        <v>-10.6098</v>
       </c>
       <c r="C4" t="n">
-        <v>-11.0642</v>
+        <v>-11.0409</v>
       </c>
       <c r="D4" t="n">
-        <v>-10.6329</v>
+        <v>-10.5447</v>
       </c>
       <c r="E4" t="n">
-        <v>-10.7224</v>
+        <v>-10.7307</v>
       </c>
       <c r="F4" t="n">
-        <v>-10.9526</v>
+        <v>-10.9357</v>
       </c>
       <c r="G4" t="n">
-        <v>-11.2165</v>
+        <v>-11.2067</v>
       </c>
       <c r="H4" t="n">
-        <v>-10.4743</v>
+        <v>-10.4782</v>
       </c>
       <c r="I4" t="n">
-        <v>-10.7711</v>
+        <v>-10.756</v>
       </c>
       <c r="J4" t="n">
-        <v>-10.9094</v>
+        <v>-10.9013</v>
       </c>
       <c r="K4" t="n">
-        <v>-10.6503</v>
+        <v>-10.6922</v>
       </c>
       <c r="L4" t="n">
-        <v>-4.262</v>
+        <v>-11.0494</v>
       </c>
       <c r="M4" t="n">
-        <v>-11.1341</v>
+        <v>-10.5629</v>
       </c>
       <c r="N4" t="n">
-        <v>-10.6088</v>
+        <v>-11.0389</v>
       </c>
       <c r="O4" t="n">
-        <v>-11.0517</v>
+        <v>-10.7288</v>
       </c>
       <c r="P4" t="n">
-        <v>-10.6791</v>
+        <v>-10.6417</v>
       </c>
       <c r="Q4" t="n">
-        <v>-10.6682</v>
+        <v>-10.7779</v>
       </c>
       <c r="R4" t="n">
-        <v>-10.8159</v>
+        <v>-10.6691</v>
       </c>
       <c r="S4" t="n">
-        <v>-10.7213</v>
+        <v>-10.6254</v>
       </c>
       <c r="T4" t="n">
-        <v>-10.62</v>
+        <v>-10.7168</v>
       </c>
       <c r="U4" t="n">
-        <v>-10.7544</v>
+        <v>-11.4282</v>
       </c>
       <c r="V4" t="n">
-        <v>-11.4273</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-11.0106</v>
+        <v>-11.0334</v>
       </c>
     </row>
     <row r="5">
@@ -801,70 +785,67 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-11.1465</v>
+        <v>-10.8636</v>
       </c>
       <c r="C5" t="n">
-        <v>-11.6466</v>
+        <v>-11.3947</v>
       </c>
       <c r="D5" t="n">
-        <v>-11.0953</v>
+        <v>-10.723</v>
       </c>
       <c r="E5" t="n">
-        <v>-10.8108</v>
+        <v>-10.894</v>
       </c>
       <c r="F5" t="n">
-        <v>-11.4849</v>
+        <v>-10.7174</v>
       </c>
       <c r="G5" t="n">
-        <v>-11.6825</v>
+        <v>-11.4802</v>
       </c>
       <c r="H5" t="n">
-        <v>-8.9215</v>
+        <v>-9.1692</v>
       </c>
       <c r="I5" t="n">
-        <v>-11.0386</v>
+        <v>-10.9038</v>
       </c>
       <c r="J5" t="n">
-        <v>-10.9748</v>
+        <v>-10.7682</v>
       </c>
       <c r="K5" t="n">
-        <v>-10.8281</v>
+        <v>-10.8471</v>
       </c>
       <c r="L5" t="n">
-        <v>-4.2775</v>
+        <v>-10.7009</v>
       </c>
       <c r="M5" t="n">
-        <v>-11.5939</v>
+        <v>-10.7864</v>
       </c>
       <c r="N5" t="n">
-        <v>-11.058</v>
+        <v>-10.9615</v>
       </c>
       <c r="O5" t="n">
-        <v>-11.2687</v>
+        <v>-10.8926</v>
       </c>
       <c r="P5" t="n">
-        <v>-10.809</v>
+        <v>-10.9701</v>
       </c>
       <c r="Q5" t="n">
-        <v>-11.2723</v>
+        <v>-10.7652</v>
       </c>
       <c r="R5" t="n">
-        <v>-11.0679</v>
+        <v>-10.8201</v>
       </c>
       <c r="S5" t="n">
-        <v>-10.925</v>
+        <v>-10.686</v>
       </c>
       <c r="T5" t="n">
-        <v>-10.6461</v>
+        <v>-11.0026</v>
       </c>
       <c r="U5" t="n">
-        <v>-11.1442</v>
+        <v>-11.7434</v>
       </c>
       <c r="V5" t="n">
-        <v>-11.7958</v>
-      </c>
-      <c r="W5" t="n">
-        <v>-11.5752</v>
+        <v>-11.3789</v>
       </c>
     </row>
     <row r="6">
@@ -877,7 +858,7 @@
         <v>-10.9099</v>
       </c>
       <c r="C6" t="n">
-        <v>-11.4205</v>
+        <v>-11.4204</v>
       </c>
       <c r="D6" t="n">
         <v>-10.9954</v>
@@ -904,39 +885,36 @@
         <v>-10.9214</v>
       </c>
       <c r="L6" t="n">
-        <v>-4.2834</v>
+        <v>-11.3412</v>
       </c>
       <c r="M6" t="n">
-        <v>-11.3412</v>
+        <v>-10.7429</v>
       </c>
       <c r="N6" t="n">
-        <v>-10.7429</v>
+        <v>-11.0009</v>
       </c>
       <c r="O6" t="n">
-        <v>-11.0009</v>
+        <v>-7.843</v>
       </c>
       <c r="P6" t="n">
-        <v>-7.843</v>
+        <v>-10.792</v>
       </c>
       <c r="Q6" t="n">
-        <v>-10.792</v>
+        <v>-10.9007</v>
       </c>
       <c r="R6" t="n">
-        <v>-10.9007</v>
+        <v>-9.447900000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>-9.447900000000001</v>
+        <v>-11.0464</v>
       </c>
       <c r="T6" t="n">
-        <v>-11.0464</v>
+        <v>-11.2067</v>
       </c>
       <c r="U6" t="n">
-        <v>-11.2067</v>
+        <v>-11.9793</v>
       </c>
       <c r="V6" t="n">
-        <v>-11.9793</v>
-      </c>
-      <c r="W6" t="n">
         <v>-11.2247</v>
       </c>
     </row>
@@ -951,7 +929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W6"/>
+  <dimension ref="A1:V6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1007,7 +985,7 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>CTR</t>
+          <t>EXP</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
@@ -1056,11 +1034,6 @@
         </is>
       </c>
       <c r="V1" t="inlineStr">
-        <is>
-          <t>EXP</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
         <is>
           <t>EXP</t>
         </is>
@@ -1124,60 +1097,55 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CTR_54</t>
+          <t>EXP_60</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>EXP_60</t>
+          <t>EXP_61</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>EXP_61</t>
+          <t>EXP_65</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>EXP_65</t>
+          <t>EXP_66</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>EXP_66</t>
+          <t>EXP_70</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>EXP_70</t>
+          <t>EXP_71</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>EXP_71</t>
+          <t>EXP_73</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>EXP_73</t>
+          <t>EXP_74</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>EXP_74</t>
+          <t>EXP_75</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>EXP_75</t>
+          <t>EXP_78</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
-        <is>
-          <t>EXP_78</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
         <is>
           <t>EXP_80</t>
         </is>
@@ -1190,70 +1158,67 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-10.5468</v>
+        <v>-10.5362</v>
       </c>
       <c r="C3" t="n">
-        <v>-10.5752</v>
+        <v>-10.6035</v>
       </c>
       <c r="D3" t="n">
-        <v>-9.5824</v>
+        <v>-9.7195</v>
       </c>
       <c r="E3" t="n">
-        <v>-10.6891</v>
+        <v>-10.6567</v>
       </c>
       <c r="F3" t="n">
-        <v>-10.4371</v>
+        <v>-10.4774</v>
       </c>
       <c r="G3" t="n">
-        <v>-11.0135</v>
+        <v>-10.99</v>
       </c>
       <c r="H3" t="n">
-        <v>-10.6029</v>
+        <v>-10.5814</v>
       </c>
       <c r="I3" t="n">
-        <v>-10.7665</v>
+        <v>-10.7724</v>
       </c>
       <c r="J3" t="n">
-        <v>-10.9333</v>
+        <v>-10.9518</v>
       </c>
       <c r="K3" t="n">
-        <v>-10.4555</v>
+        <v>-10.4761</v>
       </c>
       <c r="L3" t="n">
-        <v>-4.8617</v>
+        <v>-10.7254</v>
       </c>
       <c r="M3" t="n">
-        <v>-10.8303</v>
+        <v>-10.4162</v>
       </c>
       <c r="N3" t="n">
-        <v>-10.4034</v>
+        <v>-10.8338</v>
       </c>
       <c r="O3" t="n">
-        <v>-10.8123</v>
+        <v>-10.9207</v>
       </c>
       <c r="P3" t="n">
-        <v>-10.8972</v>
+        <v>-9.979799999999999</v>
       </c>
       <c r="Q3" t="n">
-        <v>-10.0344</v>
+        <v>-10.2289</v>
       </c>
       <c r="R3" t="n">
-        <v>-10.1815</v>
+        <v>-10.5457</v>
       </c>
       <c r="S3" t="n">
-        <v>-10.5238</v>
+        <v>-10.4528</v>
       </c>
       <c r="T3" t="n">
-        <v>-10.493</v>
+        <v>-10.0683</v>
       </c>
       <c r="U3" t="n">
-        <v>-10.0197</v>
+        <v>-11.2649</v>
       </c>
       <c r="V3" t="n">
-        <v>-11.2478</v>
-      </c>
-      <c r="W3" t="n">
-        <v>-10.8478</v>
+        <v>-10.8707</v>
       </c>
     </row>
     <row r="4">
@@ -1263,70 +1228,67 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-10.7958</v>
+        <v>-10.7753</v>
       </c>
       <c r="C4" t="n">
-        <v>-10.9042</v>
+        <v>-10.9118</v>
       </c>
       <c r="D4" t="n">
-        <v>-10.3371</v>
+        <v>-10.2926</v>
       </c>
       <c r="E4" t="n">
-        <v>-10.966</v>
+        <v>-10.9675</v>
       </c>
       <c r="F4" t="n">
-        <v>-10.7156</v>
+        <v>-10.7296</v>
       </c>
       <c r="G4" t="n">
-        <v>-11.2684</v>
+        <v>-11.2344</v>
       </c>
       <c r="H4" t="n">
-        <v>-10.7592</v>
+        <v>-10.7624</v>
       </c>
       <c r="I4" t="n">
-        <v>-11.1528</v>
+        <v>-11.1545</v>
       </c>
       <c r="J4" t="n">
-        <v>-11.282</v>
+        <v>-11.2829</v>
       </c>
       <c r="K4" t="n">
-        <v>-10.6546</v>
+        <v>-10.6776</v>
       </c>
       <c r="L4" t="n">
-        <v>-4.8455</v>
+        <v>-10.9561</v>
       </c>
       <c r="M4" t="n">
-        <v>-11.0567</v>
+        <v>-10.5832</v>
       </c>
       <c r="N4" t="n">
-        <v>-10.5808</v>
+        <v>-11.0172</v>
       </c>
       <c r="O4" t="n">
-        <v>-10.9971</v>
+        <v>-11.0427</v>
       </c>
       <c r="P4" t="n">
-        <v>-11.0039</v>
+        <v>-10.3387</v>
       </c>
       <c r="Q4" t="n">
-        <v>-10.3858</v>
+        <v>-10.5342</v>
       </c>
       <c r="R4" t="n">
-        <v>-10.5333</v>
+        <v>-10.866</v>
       </c>
       <c r="S4" t="n">
-        <v>-10.8953</v>
+        <v>-10.6776</v>
       </c>
       <c r="T4" t="n">
-        <v>-10.6874</v>
+        <v>-10.3094</v>
       </c>
       <c r="U4" t="n">
-        <v>-10.2973</v>
+        <v>-11.4524</v>
       </c>
       <c r="V4" t="n">
-        <v>-11.4436</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-11.0629</v>
+        <v>-11.0795</v>
       </c>
     </row>
     <row r="5">
@@ -1336,70 +1298,67 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-11.289</v>
+        <v>-11.0441</v>
       </c>
       <c r="C5" t="n">
-        <v>-11.5786</v>
+        <v>-11.2687</v>
       </c>
       <c r="D5" t="n">
-        <v>-10.9639</v>
+        <v>-10.6549</v>
       </c>
       <c r="E5" t="n">
-        <v>-11.4475</v>
+        <v>-11.2728</v>
       </c>
       <c r="F5" t="n">
-        <v>-11.4306</v>
+        <v>-11.0965</v>
       </c>
       <c r="G5" t="n">
-        <v>-11.7286</v>
+        <v>-11.4496</v>
       </c>
       <c r="H5" t="n">
-        <v>-9.8329</v>
+        <v>-10.0611</v>
       </c>
       <c r="I5" t="n">
-        <v>-11.466</v>
+        <v>-11.3162</v>
       </c>
       <c r="J5" t="n">
-        <v>-11.6234</v>
+        <v>-11.4072</v>
       </c>
       <c r="K5" t="n">
-        <v>-11.2474</v>
+        <v>-11.0685</v>
       </c>
       <c r="L5" t="n">
-        <v>-4.8576</v>
+        <v>-10.975</v>
       </c>
       <c r="M5" t="n">
-        <v>-11.6105</v>
+        <v>-10.8155</v>
       </c>
       <c r="N5" t="n">
-        <v>-11.0547</v>
+        <v>-11.2842</v>
       </c>
       <c r="O5" t="n">
-        <v>-11.5334</v>
+        <v>-11.301</v>
       </c>
       <c r="P5" t="n">
-        <v>-11.3089</v>
+        <v>-10.7923</v>
       </c>
       <c r="Q5" t="n">
-        <v>-11.1286</v>
+        <v>-10.4812</v>
       </c>
       <c r="R5" t="n">
-        <v>-10.9054</v>
+        <v>-11.2099</v>
       </c>
       <c r="S5" t="n">
-        <v>-11.3759</v>
+        <v>-10.8879</v>
       </c>
       <c r="T5" t="n">
-        <v>-10.9995</v>
+        <v>-10.6918</v>
       </c>
       <c r="U5" t="n">
-        <v>-10.8279</v>
+        <v>-11.7272</v>
       </c>
       <c r="V5" t="n">
-        <v>-11.8988</v>
-      </c>
-      <c r="W5" t="n">
-        <v>-11.6729</v>
+        <v>-11.3697</v>
       </c>
     </row>
     <row r="6">
@@ -1436,42 +1395,39 @@
         <v>-11.3967</v>
       </c>
       <c r="K6" t="n">
-        <v>-10.8244</v>
+        <v>-10.8243</v>
       </c>
       <c r="L6" t="n">
-        <v>-4.8627</v>
+        <v>-11.171</v>
       </c>
       <c r="M6" t="n">
-        <v>-11.171</v>
+        <v>-10.876</v>
       </c>
       <c r="N6" t="n">
-        <v>-10.876</v>
+        <v>-11.2397</v>
       </c>
       <c r="O6" t="n">
-        <v>-11.2397</v>
+        <v>-8.679600000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>-8.679600000000001</v>
+        <v>-10.7487</v>
       </c>
       <c r="Q6" t="n">
-        <v>-10.7487</v>
+        <v>-10.5498</v>
       </c>
       <c r="R6" t="n">
-        <v>-10.5498</v>
+        <v>-10.1196</v>
       </c>
       <c r="S6" t="n">
-        <v>-10.1197</v>
+        <v>-11.0661</v>
       </c>
       <c r="T6" t="n">
-        <v>-11.0661</v>
+        <v>-10.9473</v>
       </c>
       <c r="U6" t="n">
-        <v>-10.9473</v>
+        <v>-12.0007</v>
       </c>
       <c r="V6" t="n">
-        <v>-12.0007</v>
-      </c>
-      <c r="W6" t="n">
         <v>-11.2855</v>
       </c>
     </row>
@@ -1486,7 +1442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W6"/>
+  <dimension ref="A1:V6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1542,7 +1498,7 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>CTR</t>
+          <t>EXP</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
@@ -1591,11 +1547,6 @@
         </is>
       </c>
       <c r="V1" t="inlineStr">
-        <is>
-          <t>EXP</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
         <is>
           <t>EXP</t>
         </is>
@@ -1659,60 +1610,55 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CTR_54</t>
+          <t>EXP_60</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>EXP_60</t>
+          <t>EXP_61</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>EXP_61</t>
+          <t>EXP_65</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>EXP_65</t>
+          <t>EXP_66</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>EXP_66</t>
+          <t>EXP_70</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>EXP_70</t>
+          <t>EXP_71</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>EXP_71</t>
+          <t>EXP_73</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>EXP_73</t>
+          <t>EXP_74</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>EXP_74</t>
+          <t>EXP_75</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>EXP_75</t>
+          <t>EXP_78</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
-        <is>
-          <t>EXP_78</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
         <is>
           <t>EXP_80</t>
         </is>
@@ -1725,70 +1671,67 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-9.9955</v>
+        <v>-9.997299999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>-10.2975</v>
+        <v>-10.306</v>
       </c>
       <c r="D3" t="n">
-        <v>-9.6463</v>
+        <v>-9.7182</v>
       </c>
       <c r="E3" t="n">
-        <v>-10.8601</v>
+        <v>-10.8402</v>
       </c>
       <c r="F3" t="n">
-        <v>-10.52</v>
+        <v>-10.5371</v>
       </c>
       <c r="G3" t="n">
-        <v>-10.9912</v>
+        <v>-10.9283</v>
       </c>
       <c r="H3" t="n">
-        <v>-10.1604</v>
+        <v>-10.1574</v>
       </c>
       <c r="I3" t="n">
-        <v>-10.3161</v>
+        <v>-10.3341</v>
       </c>
       <c r="J3" t="n">
-        <v>-10.8613</v>
+        <v>-10.8765</v>
       </c>
       <c r="K3" t="n">
-        <v>-10.019</v>
+        <v>-10.0362</v>
       </c>
       <c r="L3" t="n">
-        <v>-5.0145</v>
+        <v>-10.2186</v>
       </c>
       <c r="M3" t="n">
-        <v>-10.2267</v>
+        <v>-9.2376</v>
       </c>
       <c r="N3" t="n">
-        <v>-9.222099999999999</v>
+        <v>-9.8247</v>
       </c>
       <c r="O3" t="n">
-        <v>-9.7875</v>
+        <v>-10.522</v>
       </c>
       <c r="P3" t="n">
-        <v>-10.5101</v>
+        <v>-9.708600000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>-9.724399999999999</v>
+        <v>-9.9147</v>
       </c>
       <c r="R3" t="n">
-        <v>-9.8985</v>
+        <v>-10.409</v>
       </c>
       <c r="S3" t="n">
-        <v>-10.4189</v>
+        <v>-9.753</v>
       </c>
       <c r="T3" t="n">
-        <v>-9.735099999999999</v>
+        <v>-9.5769</v>
       </c>
       <c r="U3" t="n">
-        <v>-9.555099999999999</v>
+        <v>-10.1247</v>
       </c>
       <c r="V3" t="n">
-        <v>-10.1175</v>
-      </c>
-      <c r="W3" t="n">
-        <v>-10.5567</v>
+        <v>-10.6054</v>
       </c>
     </row>
     <row r="4">
@@ -1798,70 +1741,67 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-10.2047</v>
+        <v>-10.1996</v>
       </c>
       <c r="C4" t="n">
-        <v>-10.5571</v>
+        <v>-10.5456</v>
       </c>
       <c r="D4" t="n">
-        <v>-10.1062</v>
+        <v>-10.0941</v>
       </c>
       <c r="E4" t="n">
-        <v>-11.0883</v>
+        <v>-11.0849</v>
       </c>
       <c r="F4" t="n">
-        <v>-10.7899</v>
+        <v>-10.7749</v>
       </c>
       <c r="G4" t="n">
-        <v>-11.1599</v>
+        <v>-11.1059</v>
       </c>
       <c r="H4" t="n">
-        <v>-10.3699</v>
+        <v>-10.371</v>
       </c>
       <c r="I4" t="n">
-        <v>-10.5758</v>
+        <v>-10.5738</v>
       </c>
       <c r="J4" t="n">
-        <v>-11.1331</v>
+        <v>-11.1157</v>
       </c>
       <c r="K4" t="n">
-        <v>-10.234</v>
+        <v>-10.2428</v>
       </c>
       <c r="L4" t="n">
-        <v>-5.0023</v>
+        <v>-10.4024</v>
       </c>
       <c r="M4" t="n">
-        <v>-10.4257</v>
+        <v>-9.3889</v>
       </c>
       <c r="N4" t="n">
-        <v>-9.3764</v>
+        <v>-10.066</v>
       </c>
       <c r="O4" t="n">
-        <v>-10.0309</v>
+        <v>-10.5933</v>
       </c>
       <c r="P4" t="n">
-        <v>-10.5797</v>
+        <v>-10.0353</v>
       </c>
       <c r="Q4" t="n">
-        <v>-10.0457</v>
+        <v>-10.1138</v>
       </c>
       <c r="R4" t="n">
-        <v>-10.1255</v>
+        <v>-10.6227</v>
       </c>
       <c r="S4" t="n">
-        <v>-10.6473</v>
+        <v>-9.872400000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>-9.853300000000001</v>
+        <v>-9.7317</v>
       </c>
       <c r="U4" t="n">
-        <v>-9.7158</v>
+        <v>-10.2945</v>
       </c>
       <c r="V4" t="n">
-        <v>-10.2912</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-10.6559</v>
+        <v>-10.6961</v>
       </c>
     </row>
     <row r="5">
@@ -1871,70 +1811,67 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-10.7107</v>
+        <v>-10.4907</v>
       </c>
       <c r="C5" t="n">
-        <v>-11.1997</v>
+        <v>-10.9063</v>
       </c>
       <c r="D5" t="n">
-        <v>-10.7533</v>
+        <v>-10.4048</v>
       </c>
       <c r="E5" t="n">
-        <v>-11.5578</v>
+        <v>-11.4331</v>
       </c>
       <c r="F5" t="n">
-        <v>-11.377</v>
+        <v>-11.0936</v>
       </c>
       <c r="G5" t="n">
-        <v>-11.6308</v>
+        <v>-11.294</v>
       </c>
       <c r="H5" t="n">
-        <v>-10.2324</v>
+        <v>-10.3692</v>
       </c>
       <c r="I5" t="n">
-        <v>-11.062</v>
+        <v>-10.8872</v>
       </c>
       <c r="J5" t="n">
-        <v>-11.602</v>
+        <v>-11.3669</v>
       </c>
       <c r="K5" t="n">
-        <v>-10.998</v>
+        <v>-10.7394</v>
       </c>
       <c r="L5" t="n">
-        <v>-5.0114</v>
+        <v>-10.6585</v>
       </c>
       <c r="M5" t="n">
-        <v>-11.1494</v>
+        <v>-9.7742</v>
       </c>
       <c r="N5" t="n">
-        <v>-9.9381</v>
+        <v>-10.7331</v>
       </c>
       <c r="O5" t="n">
-        <v>-10.9246</v>
+        <v>-10.9809</v>
       </c>
       <c r="P5" t="n">
-        <v>-10.9992</v>
+        <v>-10.6956</v>
       </c>
       <c r="Q5" t="n">
-        <v>-10.9144</v>
+        <v>-10.197</v>
       </c>
       <c r="R5" t="n">
-        <v>-10.5392</v>
+        <v>-11.0092</v>
       </c>
       <c r="S5" t="n">
-        <v>-11.2417</v>
+        <v>-10.137</v>
       </c>
       <c r="T5" t="n">
-        <v>-10.3174</v>
+        <v>-10.2912</v>
       </c>
       <c r="U5" t="n">
-        <v>-10.3422</v>
+        <v>-10.5887</v>
       </c>
       <c r="V5" t="n">
-        <v>-10.8446</v>
-      </c>
-      <c r="W5" t="n">
-        <v>-11.16</v>
+        <v>-10.8441</v>
       </c>
     </row>
     <row r="6">
@@ -1968,45 +1905,42 @@
         <v>-11.0307</v>
       </c>
       <c r="J6" t="n">
-        <v>-11.3186</v>
+        <v>-11.3185</v>
       </c>
       <c r="K6" t="n">
         <v>-10.3672</v>
       </c>
       <c r="L6" t="n">
-        <v>-5.0155</v>
+        <v>-10.5711</v>
       </c>
       <c r="M6" t="n">
-        <v>-10.5711</v>
+        <v>-9.813700000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>-9.813700000000001</v>
+        <v>-10.5548</v>
       </c>
       <c r="O6" t="n">
-        <v>-10.5548</v>
+        <v>-9.1252</v>
       </c>
       <c r="P6" t="n">
-        <v>-9.1252</v>
+        <v>-10.4969</v>
       </c>
       <c r="Q6" t="n">
-        <v>-10.4969</v>
+        <v>-10.2092</v>
       </c>
       <c r="R6" t="n">
-        <v>-10.2092</v>
+        <v>-10.4085</v>
       </c>
       <c r="S6" t="n">
-        <v>-10.4085</v>
+        <v>-10.1822</v>
       </c>
       <c r="T6" t="n">
-        <v>-10.1822</v>
+        <v>-10.5562</v>
       </c>
       <c r="U6" t="n">
-        <v>-10.5562</v>
+        <v>-10.7624</v>
       </c>
       <c r="V6" t="n">
-        <v>-10.7624</v>
-      </c>
-      <c r="W6" t="n">
         <v>-10.5068</v>
       </c>
     </row>
@@ -2021,7 +1955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W6"/>
+  <dimension ref="A1:V6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2077,7 +2011,7 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>CTR</t>
+          <t>EXP</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
@@ -2126,11 +2060,6 @@
         </is>
       </c>
       <c r="V1" t="inlineStr">
-        <is>
-          <t>EXP</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
         <is>
           <t>EXP</t>
         </is>
@@ -2194,60 +2123,55 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CTR_54</t>
+          <t>EXP_60</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>EXP_60</t>
+          <t>EXP_61</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>EXP_61</t>
+          <t>EXP_65</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>EXP_65</t>
+          <t>EXP_66</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>EXP_66</t>
+          <t>EXP_70</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>EXP_70</t>
+          <t>EXP_71</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>EXP_71</t>
+          <t>EXP_73</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>EXP_73</t>
+          <t>EXP_74</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>EXP_74</t>
+          <t>EXP_75</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>EXP_75</t>
+          <t>EXP_78</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
-        <is>
-          <t>EXP_78</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
         <is>
           <t>EXP_80</t>
         </is>
@@ -2260,70 +2184,67 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-10.2355</v>
+        <v>-10.2237</v>
       </c>
       <c r="C3" t="n">
-        <v>-10.601</v>
+        <v>-10.6188</v>
       </c>
       <c r="D3" t="n">
-        <v>-10.1321</v>
+        <v>-10.2594</v>
       </c>
       <c r="E3" t="n">
-        <v>-10.7237</v>
+        <v>-10.7199</v>
       </c>
       <c r="F3" t="n">
-        <v>-10.752</v>
+        <v>-10.6754</v>
       </c>
       <c r="G3" t="n">
-        <v>-10.9114</v>
+        <v>-10.9157</v>
       </c>
       <c r="H3" t="n">
-        <v>-10.6908</v>
+        <v>-10.6965</v>
       </c>
       <c r="I3" t="n">
-        <v>-10.8573</v>
+        <v>-10.8037</v>
       </c>
       <c r="J3" t="n">
-        <v>-10.9898</v>
+        <v>-10.9894</v>
       </c>
       <c r="K3" t="n">
-        <v>-10.8576</v>
+        <v>-10.8487</v>
       </c>
       <c r="L3" t="n">
-        <v>-4.5464</v>
+        <v>-11.0352</v>
       </c>
       <c r="M3" t="n">
-        <v>-11.1302</v>
+        <v>-9.8033</v>
       </c>
       <c r="N3" t="n">
-        <v>-9.7973</v>
+        <v>-10.9841</v>
       </c>
       <c r="O3" t="n">
-        <v>-11.0297</v>
+        <v>-11.147</v>
       </c>
       <c r="P3" t="n">
-        <v>-11.1577</v>
+        <v>-10.5454</v>
       </c>
       <c r="Q3" t="n">
-        <v>-10.5633</v>
+        <v>-10.7054</v>
       </c>
       <c r="R3" t="n">
-        <v>-10.7127</v>
+        <v>-10.3002</v>
       </c>
       <c r="S3" t="n">
-        <v>-10.2701</v>
+        <v>-10.5898</v>
       </c>
       <c r="T3" t="n">
-        <v>-10.6229</v>
+        <v>-10.6793</v>
       </c>
       <c r="U3" t="n">
-        <v>-10.6826</v>
+        <v>-10.9014</v>
       </c>
       <c r="V3" t="n">
-        <v>-10.9768</v>
-      </c>
-      <c r="W3" t="n">
-        <v>-10.8224</v>
+        <v>-10.85</v>
       </c>
     </row>
     <row r="4">
@@ -2333,70 +2254,67 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-10.3915</v>
+        <v>-10.3821</v>
       </c>
       <c r="C4" t="n">
-        <v>-10.9652</v>
+        <v>-10.9789</v>
       </c>
       <c r="D4" t="n">
-        <v>-10.9478</v>
+        <v>-10.8795</v>
       </c>
       <c r="E4" t="n">
-        <v>-10.9841</v>
+        <v>-10.9427</v>
       </c>
       <c r="F4" t="n">
-        <v>-11.0506</v>
+        <v>-10.9655</v>
       </c>
       <c r="G4" t="n">
-        <v>-11.0881</v>
+        <v>-11.0797</v>
       </c>
       <c r="H4" t="n">
-        <v>-10.8189</v>
+        <v>-10.839</v>
       </c>
       <c r="I4" t="n">
-        <v>-10.9237</v>
+        <v>-10.8446</v>
       </c>
       <c r="J4" t="n">
-        <v>-11.2802</v>
+        <v>-11.2602</v>
       </c>
       <c r="K4" t="n">
-        <v>-11.0338</v>
+        <v>-10.9842</v>
       </c>
       <c r="L4" t="n">
-        <v>-4.5367</v>
+        <v>-11.2009</v>
       </c>
       <c r="M4" t="n">
-        <v>-11.3102</v>
+        <v>-9.9352</v>
       </c>
       <c r="N4" t="n">
-        <v>-9.9475</v>
+        <v>-11.131</v>
       </c>
       <c r="O4" t="n">
-        <v>-11.1753</v>
+        <v>-11.1581</v>
       </c>
       <c r="P4" t="n">
-        <v>-11.1691</v>
+        <v>-10.6693</v>
       </c>
       <c r="Q4" t="n">
-        <v>-10.6736</v>
+        <v>-10.9443</v>
       </c>
       <c r="R4" t="n">
-        <v>-10.9536</v>
+        <v>-10.6968</v>
       </c>
       <c r="S4" t="n">
-        <v>-10.6988</v>
+        <v>-10.7544</v>
       </c>
       <c r="T4" t="n">
-        <v>-10.7448</v>
+        <v>-10.8788</v>
       </c>
       <c r="U4" t="n">
-        <v>-10.8827</v>
+        <v>-11.0546</v>
       </c>
       <c r="V4" t="n">
-        <v>-11.122</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-10.9902</v>
+        <v>-11.0013</v>
       </c>
     </row>
     <row r="5">
@@ -2406,70 +2324,67 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-10.8832</v>
+        <v>-10.6532</v>
       </c>
       <c r="C5" t="n">
-        <v>-11.6079</v>
+        <v>-11.3769</v>
       </c>
       <c r="D5" t="n">
-        <v>-11.4151</v>
+        <v>-11.0929</v>
       </c>
       <c r="E5" t="n">
-        <v>-11.5029</v>
+        <v>-11.3325</v>
       </c>
       <c r="F5" t="n">
-        <v>-11.6266</v>
+        <v>-11.3078</v>
       </c>
       <c r="G5" t="n">
-        <v>-11.6725</v>
+        <v>-11.4759</v>
       </c>
       <c r="H5" t="n">
-        <v>-10.4016</v>
+        <v>-10.5845</v>
       </c>
       <c r="I5" t="n">
-        <v>-11.3606</v>
+        <v>-11.2261</v>
       </c>
       <c r="J5" t="n">
-        <v>-11.6713</v>
+        <v>-11.4556</v>
       </c>
       <c r="K5" t="n">
-        <v>-11.4984</v>
+        <v>-11.3442</v>
       </c>
       <c r="L5" t="n">
-        <v>-4.5442</v>
+        <v>-11.4112</v>
       </c>
       <c r="M5" t="n">
-        <v>-11.7042</v>
+        <v>-10.2357</v>
       </c>
       <c r="N5" t="n">
-        <v>-10.4258</v>
+        <v>-11.1903</v>
       </c>
       <c r="O5" t="n">
-        <v>-11.4604</v>
+        <v>-11.4095</v>
       </c>
       <c r="P5" t="n">
-        <v>-11.426</v>
+        <v>-10.8518</v>
       </c>
       <c r="Q5" t="n">
-        <v>-10.9381</v>
+        <v>-11.0494</v>
       </c>
       <c r="R5" t="n">
-        <v>-11.2997</v>
+        <v>-11.2582</v>
       </c>
       <c r="S5" t="n">
-        <v>-11.377</v>
+        <v>-10.9542</v>
       </c>
       <c r="T5" t="n">
-        <v>-11.0626</v>
+        <v>-11.2228</v>
       </c>
       <c r="U5" t="n">
-        <v>-11.3589</v>
+        <v>-11.3535</v>
       </c>
       <c r="V5" t="n">
-        <v>-11.4844</v>
-      </c>
-      <c r="W5" t="n">
-        <v>-11.6669</v>
+        <v>-11.4268</v>
       </c>
     </row>
     <row r="6">
@@ -2479,7 +2394,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-10.6829</v>
+        <v>-10.6828</v>
       </c>
       <c r="C6" t="n">
         <v>-11.4362</v>
@@ -2509,39 +2424,36 @@
         <v>-11.2784</v>
       </c>
       <c r="L6" t="n">
-        <v>-4.5483</v>
+        <v>-11.364</v>
       </c>
       <c r="M6" t="n">
-        <v>-11.3641</v>
+        <v>-10.2549</v>
       </c>
       <c r="N6" t="n">
-        <v>-10.2549</v>
+        <v>-11.1915</v>
       </c>
       <c r="O6" t="n">
-        <v>-11.1915</v>
+        <v>-9.2079</v>
       </c>
       <c r="P6" t="n">
-        <v>-9.2079</v>
+        <v>-10.8429</v>
       </c>
       <c r="Q6" t="n">
-        <v>-10.8429</v>
+        <v>-11.1413</v>
       </c>
       <c r="R6" t="n">
-        <v>-11.1413</v>
+        <v>-10.4166</v>
       </c>
       <c r="S6" t="n">
-        <v>-10.4167</v>
+        <v>-11.0553</v>
       </c>
       <c r="T6" t="n">
-        <v>-11.0553</v>
+        <v>-11.3847</v>
       </c>
       <c r="U6" t="n">
-        <v>-11.3847</v>
+        <v>-11.4594</v>
       </c>
       <c r="V6" t="n">
-        <v>-11.4594</v>
-      </c>
-      <c r="W6" t="n">
         <v>-11.3841</v>
       </c>
     </row>
